--- a/docassemble/MAEvictionDefense/data/sources/eviction_pt.xlsx
+++ b/docassemble/MAEvictionDefense/data/sources/eviction_pt.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1219"/>
+  <dimension ref="A1:H1223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.7109375" customWidth="1" min="1" max="1"/>
@@ -18229,7 +18229,7 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>06affba7ad2203d850a91c6af6819f61</t>
+          <t>575ad08957cfe9bd85d7f94d8711ed35</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
@@ -18247,7 +18247,7 @@
           <t xml:space="preserve">You can continue this interview on another device, or share it with 
 someone who will help you finish it. Choose any of the options below to share
 the interview.
-Right-click and copy [this link](${interview_url()}).
+Right-click and copy [the link to your interview](${interview_url()}).
 % if device() and not device().is_mobile:
 Use your phone's camera to point at this barcode. Click the link that appears
 in the camera's viewfinder.
@@ -18263,7 +18263,7 @@
           <t xml:space="preserve">Pode continuar esta entrevista noutro dispositivo, ou partilhá-la com 
 alguém que o ajudará a terminá-lo. Escolha qualquer uma das opções abaixo para partilhar
 a entrevista.
-Clique com o botão direito do rato e copie [este link](${interview_url()}).
+Clique com o botão direito do rato e copie [o link da sua entrevista](${interview_url()}).
 % if device() and not device().is_mobile:
 Utilize a câmara do seu telefone para apontar para este código de barras. Clique no link que aparece no visor da câmara.
 &lt;center&gt;
@@ -40394,7 +40394,7 @@
       </c>
       <c r="D949" s="2" t="inlineStr">
         <is>
-          <t>405a7c1de4db0b51f49baacb5de85580</t>
+          <t>8d80904edef43f2eedc35a288289b349</t>
         </is>
       </c>
       <c r="E949" s="2" t="inlineStr">
@@ -40424,7 +40424,7 @@
   ${landlord.name}.
 % endif
 You also need to send a copy of the motion to ${court}.
-Learn more and continue the form online [here](${interview_url()}) or download
+Learn more and [continue the form online](${interview_url()}) or download
 the PDF here: https://gbls.org/tactics/compel.
 </t>
         </is>
@@ -40446,8 +40446,8 @@
   ${landlord.name}.
 % endif
 Você também precisa enviar uma cópia da moção para ${court}.
-Saiba mais e continue o formulário online [aqui](${interview_url()}) ou faça o download
-the PDF here: https://gbls.org/tactics/compel.
+Saiba mais e [continue o formulário online](${interview_url()}) ou faça o download
+do PDF aqui: https://gbls.org/tactics/compel.
 </t>
         </is>
       </c>
@@ -40725,7 +40725,7 @@
       </c>
       <c r="D955" s="2" t="inlineStr">
         <is>
-          <t>26fd8aed4ec30f78c45f916032146cd5</t>
+          <t>cec6553a0281b8bd2f9e4a1f35f60906</t>
         </is>
       </c>
       <c r="E955" s="2" t="inlineStr">
@@ -40742,7 +40742,7 @@
         <is>
           <t xml:space="preserve">Someone who was completing an interview using Massachusetts Defense for
 Eviction (MADE) sent you this link.
-Click [here](${interview_url()}) to keep working on the interview.
+[Keep working on the interview](${interview_url()}).
 </t>
         </is>
       </c>
@@ -40750,7 +40750,7 @@
         <is>
           <t xml:space="preserve">Alguém que estava completando uma entrevista utilizando o Massachusetts Defense for 
 despejo (MADE) enviou este link.
-Clique [aqui](${interview_url()}) para continuar trabalhando na entrevista.
+[Continue trabalhando na entrevista](${interview_url()}).
 </t>
         </is>
       </c>
@@ -52959,6 +52959,208 @@
         </is>
       </c>
     </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1220" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>a2beb488f5408ec32ba0f33f24c6c5e1</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>pt</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>By hand</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>Em mãos</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1221" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>dfc27ef27b631b0e7114573a439c3180</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>pt</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>By email</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>Por e-mail</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1222" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>409b1ef3ad4fe98ad063fb3026c6b250</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>pt</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>By mail</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>Pelo correio</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1223" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>966afd80841437ca4adfcf8f54bfab2a</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>pt</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You must give a copy of the forms we are working on to your landlord or their 
+attorney. 
+% if case.hearing_date_assigned:
+They need to _get_ the forms no later than 
+**${format_date(case.answer_date)}**.
+% if answer_date_is_holiday:
+Because ${case.answer_date} is ${answer_date_holiday}, you can
+deliver it the next weekday after ${answer_date_holiday}.
+% endif
+% else:
+Give a copy to your landlord or their attorney as soon as you can.
+% endif
+Deliver it in person
+if you can. If your landlord has a lawyer, you can email it to the lawyer.
+If your landlord does not have a lawyer, ask them first before you email it. 
+% if format_date(case.answer_date) == format_date(today()):
+It's too late to mail the paperwork.
+% else:
+Only mail it if you know
+your landlord will get it on or before ${format_date(case.answer_date)}.
+% endif
+</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Você precisa entregar uma cópia dos formulários em que estamos trabalhando ao seu locador ou ao 
+advogado dele. 
+% if case.hearing_date_assigned:
+Eles precisam _receber_ os formulários até, no máximo, 
+**${format_date(case.answer_date)}**.
+% if answer_date_is_holiday:
+Como ${case.answer_date} é ${answer_date_holiday}, você pode
+entregar no primeiro dia útil depois de ${answer_date_holiday}.
+% endif
+% else:
+Entregue uma cópia ao seu locador ou ao advogado dele o quanto antes.
+% endif
+Entregue pessoalmente
+se puder. Se o seu locador tiver advogado, você pode enviar por e-mail ao advogado.
+Se o seu locador não tiver advogado, peça permissão antes de enviar por e-mail. 
+% if format_date(case.answer_date) == format_date(today()):
+Já é tarde demais para enviar os documentos pelo correio.
+% else:
+Só envie pelo correio se você souber que
+o seu locador vai receber até ${format_date(case.answer_date)}.
+% endif
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
